--- a/hairdresser_forms/010_salon_consultation_form--hairdresser_forms.xlsx
+++ b/hairdresser_forms/010_salon_consultation_form--hairdresser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'curly',_'label':_'curly'}</t>
+          <t>curly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'curly', 'label': 'Curly'}</t>
+          <t>Curly</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'straight',_'label':_'straight'}</t>
+          <t>straight</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'straight', 'label': 'Straight'}</t>
+          <t>Straight</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'wavy',_'label':_'wavy'}</t>
+          <t>wavy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'wavy', 'label': 'Wavy'}</t>
+          <t>Wavy</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'fine',_'label':_'fine'}</t>
+          <t>fine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'fine', 'label': 'Fine'}</t>
+          <t>Fine</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'coarse',_'label':_'coarse'}</t>
+          <t>coarse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'coarse', 'label': 'Coarse'}</t>
+          <t>Coarse</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'bob',_'label':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'bob', 'label': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pixie',_'label':_'pixie'}</t>
+          <t>pixie</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'pixie', 'label': 'Pixie'}</t>
+          <t>Pixie</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pixie_cut',_'label':_'pixie_cut'}</t>
+          <t>pixie_cut</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'pixie_cut', 'label': 'Pixie Cut'}</t>
+          <t>Pixie Cut</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'roots',_'label':_'roots'}</t>
+          <t>roots</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'roots', 'label': 'Roots'}</t>
+          <t>Roots</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'length',_'label':_'length'}</t>
+          <t>length</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'length', 'label': 'Length'}</t>
+          <t>Length</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'color',_'label':_'color'}</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'color', 'label': 'Color'}</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'natural',_'label':_'natural'}</t>
+          <t>natural</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'natural', 'label': 'Natural'}</t>
+          <t>Natural</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'artificial',_'label':_'artificial'}</t>
+          <t>artificial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'artificial', 'label': 'Artificial'}</t>
+          <t>Artificial</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'balayage',_'label':_'balayage'}</t>
+          <t>balayage</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'balayage', 'label': 'Balayage'}</t>
+          <t>Balayage</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'round',_'label':_'round'}</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'round', 'label': 'Round'}</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'oval',_'label':_'oval'}</t>
+          <t>oval</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'oval', 'label': 'Oval'}</t>
+          <t>Oval</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'heart',_'label':_'heart'}</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'heart', 'label': 'Heart'}</t>
+          <t>Heart</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'oval',_'label':_'oval'}</t>
+          <t>oval</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'oval', 'label': 'Oval'}</t>
+          <t>Oval</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'heart',_'label':_'heart'}</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'heart', 'label': 'Heart'}</t>
+          <t>Heart</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'square',_'label':_'square'}</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'square', 'label': 'Square'}</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'fair',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'fair', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'olive',_'label':_'olive'}</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'olive', 'label': 'Olive'}</t>
+          <t>Olive</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'blue',_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'blue', 'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'brown',_'label':_'brown'}</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'brown', 'label': 'Brown'}</t>
+          <t>Brown</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'green',_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'green', 'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
